--- a/vtiger-crm-automation-a1-pro/src/test/resources/testScriptData.xlsx
+++ b/vtiger-crm-automation-a1-pro/src/test/resources/testScriptData.xlsx
@@ -7,7 +7,8 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
-    <sheet name="org" sheetId="1" r:id="rId1"/>
+    <sheet name="opp" sheetId="3" r:id="rId1"/>
+    <sheet name="org" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>orgName</t>
   </si>
@@ -46,6 +47,15 @@
   </si>
   <si>
     <t>pyspiders_</t>
+  </si>
+  <si>
+    <t>oppName</t>
+  </si>
+  <si>
+    <t>testing</t>
+  </si>
+  <si>
+    <t>development</t>
   </si>
 </sst>
 </file>
@@ -397,45 +407,29 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1"/>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1"/>
-      <c r="C3" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>9876556789</v>
-      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="3"/>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -560,4 +554,181 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="29.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>9876556789</v>
+      </c>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>